--- a/start-iids/data/reference/RP7.3_data_collection_20232025.xlsx
+++ b/start-iids/data/reference/RP7.3_data_collection_20232025.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Istruzioni" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unita" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Energia" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Moduli_TEI" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Moduli_EFA" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Moduli_EcoFA" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Moduli_SFA" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coefficienti" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AHP" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Unita" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Istruzioni" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Energia" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Moduli_TEI" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Moduli_EFA" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Moduli_EcoFA" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Moduli_SFA" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Coefficienti" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="AHP" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Periodo" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Riferimento" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,89 +477,1279 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>RP7.3 — Scheda di raccolta dati (serie 2023–2025)</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>plant</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>produzione_m2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>descrizione</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Viano — MTO</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Anno 2022 = riferimento (baseline) per le differenze dei moduli; 2023–2025 = serie di lavoro.</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Viano — MTO</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>I valori inseriti sono provvisori e in corso di consolidamento con le serie storiche definitive.</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Viano — MTO</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2382600</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Viano — MTO</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Come compilare:</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Scandiano — ibrido MTS+MTO</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>1) 'Unita': anagrafica e produzione annua (m²).</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C7" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Scandiano — ibrido MTS+MTO</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2) 'Energia': consumi primari — gas naturale (Nm³) ed energia elettrica (kWh), inclusa autoproduzione.</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C8" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Scandiano — ibrido MTS+MTO</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>3) 'Moduli_*': termini exergetici di ciascun modulo in MJ (vedi manuali -J).</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C9" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Scandiano — ibrido MTS+MTO</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>4) 'Coefficienti' e 'AHP': librerie di conversione e matrice dei pesi.</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C10" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Frassinoro — MTO</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Frassinoro — MTO</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Rigenerazione: sostituire i valori e rieseguire  python3 -m src.run_all  (stessa struttura di calcolo).</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Frassinoro — MTO</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Convenzione unità: calcolo interno in MJ; output in GJ (÷1.000). Exergia gas = chimica (b_fuel).</t>
-        </is>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C13" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Frassinoro — MTO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>plant</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>period_start</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>period_end</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>months_active</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>plant</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ref_plant</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ref_year</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ref_period_start</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ref_period_end</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>module</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>term</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>value_MJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>TEI-J</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>loss_MTS_MJ</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>37883340</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>TEI-J</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>loss_MTO_MJ</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>32832228</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>TEI-J</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>inv_MJ</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>3788334</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TEI-J</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>qual_MTS_MJ</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1262778</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>TEI-J</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>qual_MTO_MJ</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1010222</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EFA-J</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>RI_MJ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>151533360</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>EFA-J</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>IEQ_MJ</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>25255560</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>EFA-J</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>WEX_MJ</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>10102224</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>EFA-J</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>CIRC_MJ</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>7576668</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EcoFA-J</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>VA_MJ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>101022240</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>EcoFA-J</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>econ_in_MJ</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>31569450</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>EcoFA-J</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>INV_MJ</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>15153336</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SFA-J</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>SV_MJ</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>44197230</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SFA-J</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>train_MJ</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2525556</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SFA-J</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>lost_MJ</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3788334</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SFA-J</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>CO2_MJ</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>18941670</v>
       </c>
     </row>
   </sheetData>
@@ -571,74 +1763,89 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>plant</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>descrizione</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>produzione_m2</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>RP7.3 — Scheda di raccolta dati (serie 2023–2025)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>D020</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Viano — MTO</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>3800000</v>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>D060</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Scandiano — ibrido MTS+MTO</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>6400000</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Anno 2022 = riferimento (baseline) per le differenze dei moduli; 2023–2025 = serie di lavoro.</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>D240</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Frassinoro — MTO</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>5100000</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>I valori inseriti sono provvisori e in corso di consolidamento con le serie storiche definitive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Come compilare:</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>1) 'Unita': anagrafica e produzione annua (m²).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2) 'Energia': consumi primari — gas naturale (Nm³) ed energia elettrica (kWh), inclusa autoproduzione.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>3) 'Moduli_*': termini exergetici di ciascun modulo in MJ (vedi manuali -J).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>4) 'Coefficienti' e 'AHP': librerie di conversione e matrice dei pesi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Rigenerazione: sostituire i valori e rieseguire  python3 -m src.run_all  (stessa struttura di calcolo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Convenzione unità: calcolo interno in MJ; output in GJ (÷1.000). Exergia gas = chimica (b_fuel).</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -741,10 +1948,10 @@
         <v>2025</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>3510476</v>
+        <v>2201068</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>10238889</v>
+        <v>6419783</v>
       </c>
     </row>
     <row r="6">
@@ -1020,19 +2227,19 @@
         <v>2025</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>49544400</v>
+        <v>31064339</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>42938480</v>
+        <v>26922427</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>5063196</v>
+        <v>3174624</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1723984</v>
+        <v>1080938</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>1379187</v>
+        <v>864750</v>
       </c>
     </row>
     <row r="6">
@@ -1365,16 +2572,16 @@
         <v>2025</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>237329760</v>
+        <v>148805760</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>36654800</v>
+        <v>22982560</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>13211840</v>
+        <v>8283824</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>15346680</v>
+        <v>9622368</v>
       </c>
     </row>
     <row r="6">
@@ -1668,13 +2875,13 @@
         <v>2025</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>169820480</v>
+        <v>106477441</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>45818500</v>
+        <v>28728200</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>21122832</v>
+        <v>13244016</v>
       </c>
     </row>
     <row r="6">
@@ -1959,16 +3166,16 @@
         <v>2025</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>74296460</v>
+        <v>46583880</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>4898048</v>
+        <v>3071076</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>4954440</v>
+        <v>3106434</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>25859760</v>
+        <v>16214070</v>
       </c>
     </row>
     <row r="6">

--- a/start-iids/data/reference/RP7.3_data_collection_20232025.xlsx
+++ b/start-iids/data/reference/RP7.3_data_collection_20232025.xlsx
@@ -566,7 +566,7 @@
         <v>2025</v>
       </c>
       <c r="C5" t="n">
-        <v>2382600</v>
+        <v>2317845</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>37883340</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>32832228</v>
+        <v>33624810</v>
       </c>
     </row>
     <row r="4">
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3788334</v>
+        <v>3905420</v>
       </c>
     </row>
     <row r="5">
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1262778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1010222</v>
+        <v>1048690</v>
       </c>
     </row>
     <row r="7">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>151533360</v>
+        <v>154832760</v>
       </c>
     </row>
     <row r="8">
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>25255560</v>
+        <v>25684730</v>
       </c>
     </row>
     <row r="9">
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>10102224</v>
+        <v>10684250</v>
       </c>
     </row>
     <row r="10">
@@ -1462,7 +1462,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>7576668</v>
+        <v>7842560</v>
       </c>
     </row>
     <row r="11">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>101022240</v>
+        <v>103285400</v>
       </c>
     </row>
     <row r="12">
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>31569450</v>
+        <v>32481760</v>
       </c>
     </row>
     <row r="13">
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>15153336</v>
+        <v>15892330</v>
       </c>
     </row>
     <row r="14">
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>44197230</v>
+        <v>45638400</v>
       </c>
     </row>
     <row r="15">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2525556</v>
+        <v>2634780</v>
       </c>
     </row>
     <row r="16">
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3788334</v>
+        <v>3982560</v>
       </c>
     </row>
     <row r="17">
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>18941670</v>
+        <v>19745320</v>
       </c>
     </row>
   </sheetData>
@@ -1948,10 +1948,10 @@
         <v>2025</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2201068</v>
+        <v>2189640</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>6419783</v>
+        <v>6395870</v>
       </c>
     </row>
     <row r="6">
@@ -2227,19 +2227,19 @@
         <v>2025</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>31064339</v>
+        <v>0</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>26922427</v>
+        <v>26718940</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>3174624</v>
+        <v>2965380</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1080938</v>
+        <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>864750</v>
+        <v>752660</v>
       </c>
     </row>
     <row r="6">
@@ -2572,16 +2572,16 @@
         <v>2025</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>148805760</v>
+        <v>143956480</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>22982560</v>
+        <v>22146980</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>8283824</v>
+        <v>8012430</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>9622368</v>
+        <v>9214780</v>
       </c>
     </row>
     <row r="6">
@@ -2875,13 +2875,13 @@
         <v>2025</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>106477441</v>
+        <v>101746200</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>28728200</v>
+        <v>29364590</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>13244016</v>
+        <v>12734680</v>
       </c>
     </row>
     <row r="6">
@@ -3166,16 +3166,16 @@
         <v>2025</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>46583880</v>
+        <v>44927700</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>3071076</v>
+        <v>2972460</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>3106434</v>
+        <v>3126880</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>16214070</v>
+        <v>16886450</v>
       </c>
     </row>
     <row r="6">

--- a/start-iids/data/reference/RP7.3_data_collection_20232025.xlsx
+++ b/start-iids/data/reference/RP7.3_data_collection_20232025.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Istruzioni" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unita" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Energia" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Moduli_TEI" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Moduli_EFA" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Moduli_EcoFA" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Moduli_SFA" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coefficienti" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AHP" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Unita" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Istruzioni" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Energia" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Moduli_TEI" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Moduli_EFA" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Moduli_EcoFA" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Moduli_SFA" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Coefficienti" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="AHP" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Periodo" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Riferimento" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,89 +477,1279 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>RP7.3 — Scheda di raccolta dati (serie 2023–2025)</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>plant</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>produzione_m2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>descrizione</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Viano — MTO</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Anno 2022 = riferimento (baseline) per le differenze dei moduli; 2023–2025 = serie di lavoro.</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Viano — MTO</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>I valori inseriti sono provvisori e in corso di consolidamento con le serie storiche definitive.</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Viano — MTO</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2317845</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Viano — MTO</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Come compilare:</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Scandiano — ibrido MTS+MTO</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>1) 'Unita': anagrafica e produzione annua (m²).</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C7" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Scandiano — ibrido MTS+MTO</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2) 'Energia': consumi primari — gas naturale (Nm³) ed energia elettrica (kWh), inclusa autoproduzione.</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C8" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Scandiano — ibrido MTS+MTO</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>3) 'Moduli_*': termini exergetici di ciascun modulo in MJ (vedi manuali -J).</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C9" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Scandiano — ibrido MTS+MTO</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>4) 'Coefficienti' e 'AHP': librerie di conversione e matrice dei pesi.</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C10" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Frassinoro — MTO</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Frassinoro — MTO</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Rigenerazione: sostituire i valori e rieseguire  python3 -m src.run_all  (stessa struttura di calcolo).</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Frassinoro — MTO</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Convenzione unità: calcolo interno in MJ; output in GJ (÷1.000). Exergia gas = chimica (b_fuel).</t>
-        </is>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C13" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Frassinoro — MTO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>plant</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>period_start</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>period_end</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>months_active</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>plant</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ref_plant</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ref_year</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ref_period_start</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ref_period_end</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>module</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>term</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>value_MJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>TEI-J</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>loss_MTS_MJ</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>TEI-J</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>loss_MTO_MJ</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>33624810</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>TEI-J</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>inv_MJ</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>3905420</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TEI-J</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>qual_MTS_MJ</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>TEI-J</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>qual_MTO_MJ</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1048690</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EFA-J</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>RI_MJ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>154832760</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>EFA-J</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>IEQ_MJ</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>25684730</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>EFA-J</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>WEX_MJ</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>10684250</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>EFA-J</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>CIRC_MJ</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>7842560</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EcoFA-J</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>VA_MJ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>103285400</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>EcoFA-J</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>econ_in_MJ</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>32481760</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>EcoFA-J</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>INV_MJ</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>15892330</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SFA-J</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>SV_MJ</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>45638400</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SFA-J</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>train_MJ</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2634780</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SFA-J</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>lost_MJ</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3982560</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SFA-J</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>CO2_MJ</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>19745320</v>
       </c>
     </row>
   </sheetData>
@@ -571,74 +1763,89 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>plant</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>descrizione</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>produzione_m2</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>RP7.3 — Scheda di raccolta dati (serie 2023–2025)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>D020</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Viano — MTO</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>3800000</v>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>D060</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Scandiano — ibrido MTS+MTO</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>6400000</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Anno 2022 = riferimento (baseline) per le differenze dei moduli; 2023–2025 = serie di lavoro.</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>D240</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Frassinoro — MTO</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>5100000</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>I valori inseriti sono provvisori e in corso di consolidamento con le serie storiche definitive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Come compilare:</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>1) 'Unita': anagrafica e produzione annua (m²).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2) 'Energia': consumi primari — gas naturale (Nm³) ed energia elettrica (kWh), inclusa autoproduzione.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>3) 'Moduli_*': termini exergetici di ciascun modulo in MJ (vedi manuali -J).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>4) 'Coefficienti' e 'AHP': librerie di conversione e matrice dei pesi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Rigenerazione: sostituire i valori e rieseguire  python3 -m src.run_all  (stessa struttura di calcolo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Convenzione unità: calcolo interno in MJ; output in GJ (÷1.000). Exergia gas = chimica (b_fuel).</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -741,10 +1948,10 @@
         <v>2025</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>3510476</v>
+        <v>2189640</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>10238889</v>
+        <v>6395870</v>
       </c>
     </row>
     <row r="6">
@@ -1020,19 +2227,19 @@
         <v>2025</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>49544400</v>
+        <v>0</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>42938480</v>
+        <v>26718940</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>5063196</v>
+        <v>2965380</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1723984</v>
+        <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>1379187</v>
+        <v>752660</v>
       </c>
     </row>
     <row r="6">
@@ -1365,16 +2572,16 @@
         <v>2025</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>237329760</v>
+        <v>143956480</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>36654800</v>
+        <v>22146980</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>13211840</v>
+        <v>8012430</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>15346680</v>
+        <v>9214780</v>
       </c>
     </row>
     <row r="6">
@@ -1668,13 +2875,13 @@
         <v>2025</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>169820480</v>
+        <v>101746200</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>45818500</v>
+        <v>29364590</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>21122832</v>
+        <v>12734680</v>
       </c>
     </row>
     <row r="6">
@@ -1959,16 +3166,16 @@
         <v>2025</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>74296460</v>
+        <v>44927700</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>4898048</v>
+        <v>2972460</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>4954440</v>
+        <v>3126880</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>25859760</v>
+        <v>16886450</v>
       </c>
     </row>
     <row r="6">
